--- a/reports/二级子公司C_利润表_2026-08.xlsx
+++ b/reports/二级子公司C_利润表_2026-08.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>101689840</v>
+        <v>104220255</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>98748160</v>
+        <v>98971898</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>685914080</v>
+        <v>686266262</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>461440</v>
+        <v>459636</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3320720</v>
+        <v>3319409</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>403760</v>
+        <v>403074</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2905630</v>
+        <v>2904879</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>346080</v>
+        <v>346361</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2490540</v>
+        <v>2490349</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>323008</v>
+        <v>324035</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2324504</v>
+        <v>2324779</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>173040</v>
+        <v>173903</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1245270</v>
+        <v>1245635</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>138432</v>
+        <v>139251</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>996216</v>
+        <v>996630</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>99844080</v>
+        <v>102373995</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>96902400</v>
+        <v>97125638</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>92288000</v>
+        <v>92538870</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>639424000</v>
+        <v>639788094</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1384320</v>
+        <v>1384715</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>9962160</v>
+        <v>9963746</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>922880</v>
+        <v>920851</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6641440</v>
+        <v>6641210</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3460800</v>
+        <v>3445938</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>24905400</v>
+        <v>24899872</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>461440</v>
+        <v>458840</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>3320720</v>
+        <v>3319491</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>346080</v>
+        <v>344009</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2490540</v>
+        <v>2489410</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>576800</v>
+        <v>573754</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4150900</v>
+        <v>4149000</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>692160</v>
+        <v>689636</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4981080</v>
+        <v>4979185</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2884000</v>
+        <v>2880042</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>20754500</v>
+        <v>20749594</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>57680</v>
+        <v>51559</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>415090</v>
+        <v>412067</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1389109</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>9963591</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>927647</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6643518</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>73726576</v>
+        <v>78979434</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>66170496</v>
+        <v>66462400</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>64786176</v>
+        <v>65074739</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>441291552</v>
+        <v>441524170</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1384320</v>
+        <v>1387661</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>9962160</v>
+        <v>9965204</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2307080</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>16605831</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>736452</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5312830</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>459353</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3319907</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>550548</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3983326</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>412825</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2987276</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>275449</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1991533</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>229942</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1659756</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1038240</v>
+        <v>1037159</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>7471620</v>
+        <v>7470027</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>807520</v>
+        <v>808710</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5811260</v>
+        <v>5811117</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>692160</v>
+        <v>694741</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4981080</v>
+        <v>4981919</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>5191200</v>
+        <v>5218865</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>37358100</v>
+        <v>37370499</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>230720</v>
+        <v>232102</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1660360</v>
+        <v>1661085</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>403760</v>
+        <v>362518</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2905630</v>
+        <v>2885093</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>461440</v>
+        <v>362518</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3320720</v>
+        <v>2885093</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>57680</v>
+        <v>51608</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>415090</v>
+        <v>412033</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>185328</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1483042</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>402625</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2905379</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>123014</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>988411</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>92159</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>741270</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>153589</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1235488</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>573958</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4149055</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>82145</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>659096</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>61756</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>494413</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>103185</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>824170</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>72388</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>577002</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51782</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>412176</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>41447</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>329744</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>31069</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>247291</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26117504</v>
+        <v>24762357</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31366384</v>
+        <v>28638855</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>230553</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1660500</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51340</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>411879</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>92288</v>
+        <v>81993</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>664144</v>
+        <v>658933</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26025216</v>
+        <v>24910917</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>3230080</v>
+        <v>2867196</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>23245040</v>
+        <v>23062641</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>22795136</v>
+        <v>22043721</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>22795136</v>
+        <v>22043721</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>22795136</v>
+        <v>22043721</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>22795136</v>
+        <v>22043721</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>22795136</v>
+        <v>22043721</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
